--- a/output/pdf_financials_xlsx/RVG.xlsx
+++ b/output/pdf_financials_xlsx/RVG.xlsx
@@ -5584,34 +5584,34 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>-0.006661</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>-0.050398</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.058798</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-0.08734599999999999</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>-0.077947</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>-0.087071</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>-0.087158</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-0.087661</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>-0.002071</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>0.001223</v>
       </c>
       <c r="L91" s="3" t="n">
         <v>0.215465</v>
@@ -5648,43 +5648,43 @@
         <v>0.046657</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.123597</v>
+        <v>0.593597</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.177029</v>
+        <v>0.850696</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.252134</v>
+        <v>0.6248010000000001</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0.264048</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.281268</v>
+        <v>1.082565</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>1.157414</v>
+        <v>5.914406</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>1.957858</v>
+        <v>7.16164</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>2.686567</v>
+        <v>3.699014</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>6.255461</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>5.318912</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>5.980513</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>7.795194</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>7.307387</v>
       </c>
     </row>
     <row r="93">
@@ -9242,7 +9242,11 @@
           <t>Warrant reserve (note 13)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -9316,7 +9320,11 @@
           <t>Share-based payment reserve (note 14)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -10190,7 +10198,11 @@
           <t>Warrant reserve (note 12)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -10276,7 +10288,11 @@
           <t>Share-based payment reserve (note 13)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -10444,7 +10460,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>-0.006661</v>
       </c>
@@ -11190,7 +11210,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RVG.xlsx
+++ b/output/pdf_financials_xlsx/RVG.xlsx
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>0.146059</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>0.152817</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>0.169394</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.146059</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.152817</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.169394</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
@@ -944,13 +944,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-0.146059</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-0.152817</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>-0.169394</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
@@ -4232,52 +4232,52 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.008094</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.284821</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.07113700000000001</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.026963</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.239563</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.268186</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.166462</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.06315900000000001</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.201616</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.216511</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.462418</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.044563</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.036238</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.140892</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>1.307745</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>1.249057</v>
       </c>
     </row>
     <row r="68">
@@ -6660,7 +6660,7 @@
         <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.03497</v>
       </c>
       <c r="K111" s="3" t="n">
         <v>0</v>
@@ -7961,7 +7961,7 @@
         <v>0</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.03497</v>
       </c>
       <c r="K134" s="3" t="n">
         <v>0</v>
@@ -8016,7 +8016,7 @@
         <v>-0.487678</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-3.982648</v>
+        <v>-4.017618</v>
       </c>
       <c r="K135" s="3" t="n">
         <v>-6.133047</v>
@@ -12324,7 +12324,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -14434,7 +14438,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -14868,7 +14876,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -15500,7 +15512,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -18448,7 +18464,11 @@
           <t>Proceeds from units issued in private placement</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -18926,7 +18946,11 @@
           <t>Finder's warrants issued in private placement $</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -26300,7 +26324,11 @@
           <t>Salaries and director fees (note 19)</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -26780,7 +26808,11 @@
           <t>Directors fees (note 19)</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E208" s="5" t="n">
         <v>0.146059</v>
       </c>
